--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-0203.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-0203.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -588,7 +588,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -600,7 +602,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -612,7 +616,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -624,7 +630,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -636,7 +644,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -648,7 +658,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -660,7 +672,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -672,7 +686,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -684,7 +700,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -696,7 +714,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -708,7 +728,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -720,7 +742,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -732,7 +756,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -744,7 +770,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -756,7 +784,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -768,7 +798,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -780,7 +812,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-0203.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-0203.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -588,9 +588,7 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>44</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -602,9 +600,7 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>46</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -616,9 +612,7 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>48</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -630,9 +624,7 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>50</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -644,9 +636,7 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>52</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -658,9 +648,7 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>54</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -672,9 +660,7 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>56</v>
-      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -686,9 +672,7 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>58</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -700,9 +684,7 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>60</v>
-      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -714,9 +696,7 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -728,9 +708,7 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>64</v>
-      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -742,9 +720,7 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" t="s" s="2">
-        <v>66</v>
-      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -756,9 +732,7 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>68</v>
-      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -770,9 +744,7 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" t="s" s="2">
-        <v>70</v>
-      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -784,9 +756,7 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" t="s" s="2">
-        <v>72</v>
-      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -798,9 +768,7 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>74</v>
-      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -812,9 +780,7 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="D18" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-0203.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-0203.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="80">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Level</t>
@@ -154,6 +154,15 @@
   </si>
   <si>
     <t>N° RPPS</t>
+  </si>
+  <si>
+    <t>RPPSRG</t>
+  </si>
+  <si>
+    <t>N° RPPS Rang</t>
+  </si>
+  <si>
+    <t>N° RPPS Rang d'identification des cabinets libéraux selon le référentiel RPPS</t>
   </si>
   <si>
     <t>IDNPS</t>
@@ -561,7 +570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -588,7 +597,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -600,7 +611,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -612,175 +625,219 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>53</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>65</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
         <v>42</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
